--- a/ML-Entrees/ig/StructureDefinition-fr-lm-medication.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T09:43:36+00:00</t>
+    <t>2026-04-08T13:03:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Produit de santé</t>
+    <t>Entrée Produit de santé</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-medication.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-medication.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="175">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T13:03:38+00:00</t>
+    <t>2026-04-08T14:07:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -250,195 +250,192 @@
     <t>Base</t>
   </si>
   <si>
-    <t>fr-lm-medication.medicament</t>
+    <t>fr-lm-medication.identifyingCode[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Code du produit de santé. Non présent pour les préparations magistrales.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>fr-lm-medication.identifyingCode[x].id</t>
   </si>
   <si>
     <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>fr-lm-medication.identifyingCode[x].extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>fr-lm-medication.identifyingCode[x].coding</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>fr-lm-medication.identifyingCode[x].text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>fr-lm-medication.identifyingCode[x].identifyingCodeCodeableConcept</t>
+  </si>
+  <si>
+    <t>Codes du médicament dans une termino spécifique</t>
+  </si>
+  <si>
+    <t>fr-lm-medication.identifyingCode[x].identifyingCodeIdentifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>identifiant du medication définition</t>
+  </si>
+  <si>
+    <t>fr-lm-medication.classification</t>
+  </si>
+  <si>
+    <t>Classification ATC</t>
+  </si>
+  <si>
+    <t>fr-lm-medication.productName</t>
+  </si>
+  <si>
+    <t>Nom du produit (contenant aussi le dosage et la forme galénique). Si le médicament est codé, le nom du produit peut ne pas être renseigné.</t>
+  </si>
+  <si>
+    <t>fr-lm-medication.marketingAuthorisationHolder</t>
   </si>
   <si>
     <t xml:space="preserve">Base
 </t>
   </si>
   <si>
-    <t>Médicament</t>
-  </si>
-  <si>
-    <t>fr-lm-medication.medicament.codeProduit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Code du produit de santé</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
-    <t>fr-lm-medication.medicament.codeProduit.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>fr-lm-medication.medicament.codeProduit.extension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>fr-lm-medication.medicament.codeProduit.coding</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>fr-lm-medication.medicament.codeProduit.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>fr-lm-medication.medicament.codeProduit.identifyingCodeCodeableConcept</t>
-  </si>
-  <si>
-    <t>Codes du médicament dans une termino spécifique</t>
-  </si>
-  <si>
-    <t>fr-lm-medication.medicament.codeProduit.identifyingCodeIdentifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>identifiant du medication définition</t>
-  </si>
-  <si>
-    <t>fr-lm-medication.medicament.classificationATC</t>
-  </si>
-  <si>
-    <t>Code de regroupement ATC</t>
-  </si>
-  <si>
-    <t>fr-lm-medication.medicament.nomProduit</t>
-  </si>
-  <si>
-    <t>Nom du produit (contenant aussi le dosage et la forme galénique). Si le médicament est codé, le nom du produit peut ne pas être renseigné.</t>
-  </si>
-  <si>
-    <t>fr-lm-medication.medicament.porteurAutorisation</t>
-  </si>
-  <si>
     <t>Titulaire de l'autorisation de mise sur le marché du médicament. 
   Cette information est utile pour identifier précisément le produit. Si le produit ne dispose pas d'une autorisation de mise sur le marché, les informations fournies par le fabricant peuvent être utilisées.</t>
   </si>
   <si>
-    <t>fr-lm-medication.medicament.porteurAutorisation.nomPorteurAutorisation</t>
+    <t>fr-lm-medication.marketingAuthorisationHolder.organisationName</t>
   </si>
   <si>
     <t>Nom de l'organisme détenant l'autorisation de commercialisation/fabrication.</t>
   </si>
   <si>
-    <t>fr-lm-medication.medicament.porteurAutorisation.identifiantPorteurAutorisation</t>
+    <t>fr-lm-medication.marketingAuthorisationHolder.organisationIdentifier</t>
   </si>
   <si>
     <t>Identifiant de l'organisation et/ou de son emplacement physique.</t>
   </si>
   <si>
-    <t>fr-lm-medication.medicament.item</t>
-  </si>
-  <si>
-    <t>Dans le cas de conditionnements combinés, il peut s'agir de plusieurs produits fabriqués, chacun disposant de sa propre forme pharmaceutique ainsi que de ses ingrédients et de leurs dosages définis.</t>
-  </si>
-  <si>
-    <t>fr-lm-medication.medicament.item.formeGalenique</t>
+    <t>fr-lm-medication.item</t>
+  </si>
+  <si>
+    <t>Dans le cas de conditionnements combinés, chaque ingrédient dispose de sa propre forme galénique, ses propres ingrédients et leurs dosages respectifs.</t>
+  </si>
+  <si>
+    <t>fr-lm-medication.item.doseForm</t>
   </si>
   <si>
     <t>Forme galénique du produit de santé. EDQM Standard Terms (0.4.0.127.0.16.1.1.2.1) / classe PDF (forme galénique).</t>
   </si>
   <si>
-    <t>fr-lm-medication.medicament.item.ingredient</t>
+    <t>EDQM Standard Terms</t>
+  </si>
+  <si>
+    <t>fr-lm-medication.item.ingredient</t>
   </si>
   <si>
     <t>Substance active</t>
   </si>
   <si>
-    <t>fr-lm-medication.medicament.item.ingredient.isActive</t>
+    <t>fr-lm-medication.item.ingredient.isActive</t>
   </si>
   <si>
     <t xml:space="preserve">boolean
@@ -448,19 +445,22 @@
     <t>Indique si l'ingrédient est considéré comme un ingrédient actif. Les excipients ne sont généralement pas nécessaires et, par défaut, seuls les ingrédients actifs sont attendus.</t>
   </si>
   <si>
-    <t>fr-lm-medication.medicament.item.ingredient.substance</t>
-  </si>
-  <si>
-    <t>Substance =&gt; code SMS (2.16.840.1.113883.3.6905.2) de la substance active de l’European Medicines Agency (EMA)</t>
-  </si>
-  <si>
-    <t>fr-lm-medication.medicament.item.ingredient.infoConcentration</t>
+    <t>fr-lm-medication.item.ingredient.substance</t>
+  </si>
+  <si>
+    <t>Substance. Code SMS (2.16.840.1.113883.3.6905.2) de la substance active de l’European Medicines Agency (EMA)</t>
+  </si>
+  <si>
+    <t>SMS (2.16.840.1.113883.3.6905.2)</t>
+  </si>
+  <si>
+    <t>fr-lm-medication.item.ingredient.strength</t>
   </si>
   <si>
     <t>concentration par unité</t>
   </si>
   <si>
-    <t>fr-lm-medication.medicament.item.ingredient.infoConcentration.concentation</t>
+    <t>fr-lm-medication.item.ingredient.strength.strength</t>
   </si>
   <si>
     <t xml:space="preserve">Ratio
@@ -470,13 +470,13 @@
     <t>numérateur/dénominateur. Ex 100 mg/1 ml ou 500 mg / comprimé.</t>
   </si>
   <si>
-    <t>fr-lm-medication.medicament.item.ingredient.infoConcentration.substanceReferenceConcentration</t>
-  </si>
-  <si>
-    <t>à vérifier</t>
-  </si>
-  <si>
-    <t>fr-lm-medication.medicament.item.ingredient.quantiteItem</t>
+    <t>fr-lm-medication.item.ingredient.strength.basisOfStrengthSubstance</t>
+  </si>
+  <si>
+    <t>Concentration de référence d’une substance</t>
+  </si>
+  <si>
+    <t>fr-lm-medication.item.containedQuantity</t>
   </si>
   <si>
     <t xml:space="preserve">Quantity
@@ -486,25 +486,25 @@
     <t>quantité pour 1 item</t>
   </si>
   <si>
-    <t>fr-lm-medication.medicament.item.ingredient.conditionnement</t>
+    <t>fr-lm-medication.item.packageType</t>
   </si>
   <si>
     <t>Conditionnement primaire (ampoule, bouteille,…) EDQM Standard Terms (0.4.0.127.0.16.1.1.2.1) / classe CON (Récipient) =&gt; ampoule, blister.</t>
   </si>
   <si>
-    <t>fr-lm-medication.medicament.device</t>
+    <t>fr-lm-medication.device</t>
   </si>
   <si>
     <t>Dispositif d'administration inclus dans le produit. Les dispositifs qui ne sont pas contenus dans le conditionnement du médicament ne sont pas pris en compte.</t>
   </si>
   <si>
-    <t>fr-lm-medication.medicament.device.deviceQuantity</t>
+    <t>fr-lm-medication.device.deviceQuantity</t>
   </si>
   <si>
     <t>Nombre de dispositifs.</t>
   </si>
   <si>
-    <t>fr-lm-medication.medicament.device.device[x]</t>
+    <t>fr-lm-medication.device.device[x]</t>
   </si>
   <si>
     <t>CodeableConcept
@@ -514,19 +514,19 @@
     <t>Dispositif codé.</t>
   </si>
   <si>
-    <t>fr-lm-medication.medicament.characteristic</t>
+    <t>fr-lm-medication.characteristic</t>
   </si>
   <si>
     <t>Caractéristiques supplémentaires du produit (par ex. sans sucre, bouchon facile à ouvrir, dosage gradué). Il est prévu que les implémenteurs définissent un ensemble de valeurs (ValueSet) adapté à leurs cas d’usage.</t>
   </si>
   <si>
-    <t>fr-lm-medication.medicament.characteristic.type</t>
+    <t>fr-lm-medication.characteristic.type</t>
   </si>
   <si>
     <t>Type de caractéristique</t>
   </si>
   <si>
-    <t>fr-lm-medication.medicament.characteristic.value[x]</t>
+    <t>fr-lm-medication.characteristic.value[x]</t>
   </si>
   <si>
     <t>boolean
@@ -536,19 +536,19 @@
     <t>Valeur de la caractéristique</t>
   </si>
   <si>
-    <t>fr-lm-medication.medicament.batch</t>
+    <t>fr-lm-medication.batch</t>
   </si>
   <si>
     <t>Informations relatives au lot d’un médicament. Elles sont généralement enregistrées lors de la dispensation ou de l’administration et sont rarement connues ou pertinentes dans le cadre d’une ordonnance ou d’une demande.</t>
   </si>
   <si>
-    <t>fr-lm-medication.medicament.batch.numeroLot</t>
+    <t>fr-lm-medication.batch.lotNumber</t>
   </si>
   <si>
     <t>Numéro de lot</t>
   </si>
   <si>
-    <t>fr-lm-medication.medicament.batch.dateExpiration</t>
+    <t>fr-lm-medication.batch.expirationDate</t>
   </si>
   <si>
     <t xml:space="preserve">dateTime
@@ -857,11 +857,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ34"/>
+  <dimension ref="A1:AJ33"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="79.1875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="79.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="55.7890625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="55.7890625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -884,14 +884,14 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="28.46875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="79.1875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="55.7890625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1120,28 +1120,28 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K3" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="G3" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H3" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="L3" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="M3" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1195,16 +1195,16 @@
         <v>78</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4">
@@ -1223,7 +1223,7 @@
         <v>74</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>73</v>
@@ -1235,13 +1235,13 @@
         <v>73</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1292,38 +1292,38 @@
         <v>73</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>73</v>
@@ -1335,15 +1335,17 @@
         <v>73</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="N5" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N5" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>73</v>
@@ -1380,43 +1382,43 @@
         <v>73</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD5" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -1432,21 +1434,23 @@
         <v>73</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="O6" s="2"/>
+        <v>104</v>
+      </c>
+      <c r="O6" t="s" s="2">
+        <v>105</v>
+      </c>
       <c r="P6" t="s" s="2">
         <v>73</v>
       </c>
@@ -1482,19 +1486,19 @@
         <v>73</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>74</v>
@@ -1506,15 +1510,15 @@
         <v>73</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1525,7 +1529,7 @@
         <v>74</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>73</v>
@@ -1534,22 +1538,22 @@
         <v>73</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="O7" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="P7" t="s" s="2">
         <v>73</v>
@@ -1598,27 +1602,27 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1629,32 +1633,28 @@
         <v>74</v>
       </c>
       <c r="G8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K8" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="H8" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I8" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J8" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="K8" t="s" s="2">
-        <v>87</v>
-      </c>
       <c r="L8" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O8" t="s" s="2">
         <v>114</v>
       </c>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
         <v>73</v>
       </c>
@@ -1702,27 +1702,27 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1733,7 +1733,7 @@
         <v>74</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>73</v>
@@ -1745,7 +1745,7 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="L9" t="s" s="2">
         <v>117</v>
@@ -1802,13 +1802,13 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>73</v>
@@ -1845,13 +1845,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L10" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="L10" t="s" s="2">
-        <v>120</v>
-      </c>
       <c r="M10" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1919,10 +1919,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1933,7 +1933,7 @@
         <v>74</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>73</v>
@@ -1945,13 +1945,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2002,13 +2002,13 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>73</v>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2033,7 +2033,7 @@
         <v>74</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>73</v>
@@ -2045,7 +2045,7 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="L12" t="s" s="2">
         <v>124</v>
@@ -2102,13 +2102,13 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>73</v>
@@ -2133,7 +2133,7 @@
         <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>73</v>
@@ -2145,7 +2145,7 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L13" t="s" s="2">
         <v>126</v>
@@ -2208,7 +2208,7 @@
         <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>73</v>
@@ -2233,7 +2233,7 @@
         <v>74</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>73</v>
@@ -2245,7 +2245,7 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>128</v>
@@ -2308,7 +2308,7 @@
         <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>73</v>
@@ -2345,7 +2345,7 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="L15" t="s" s="2">
         <v>130</v>
@@ -2433,7 +2433,7 @@
         <v>74</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>73</v>
@@ -2445,7 +2445,7 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>132</v>
@@ -2481,7 +2481,7 @@
         <v>73</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="Z16" t="s" s="2">
         <v>73</v>
@@ -2508,7 +2508,7 @@
         <v>74</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>73</v>
@@ -2519,10 +2519,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2530,10 +2530,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>73</v>
@@ -2545,13 +2545,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2602,13 +2602,13 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>73</v>
@@ -2619,10 +2619,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2630,10 +2630,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>73</v>
@@ -2645,13 +2645,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2702,13 +2702,13 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>73</v>
@@ -2719,10 +2719,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2730,28 +2730,28 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K19" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="H19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K19" t="s" s="2">
-        <v>138</v>
-      </c>
       <c r="L19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2781,7 +2781,7 @@
         <v>73</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>73</v>
+        <v>141</v>
       </c>
       <c r="Z19" t="s" s="2">
         <v>73</v>
@@ -2802,13 +2802,13 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>73</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2830,10 +2830,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>73</v>
@@ -2845,13 +2845,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2902,13 +2902,13 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>73</v>
@@ -2919,10 +2919,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2930,10 +2930,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>73</v>
@@ -2945,13 +2945,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>80</v>
+        <v>145</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3002,13 +3002,13 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>73</v>
@@ -3019,10 +3019,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3030,28 +3030,28 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K22" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="G22" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K22" t="s" s="2">
-        <v>145</v>
-      </c>
       <c r="L22" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3102,13 +3102,13 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>73</v>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3133,7 +3133,7 @@
         <v>74</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>73</v>
@@ -3145,13 +3145,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3202,13 +3202,13 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>73</v>
@@ -3219,10 +3219,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3233,7 +3233,7 @@
         <v>74</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>73</v>
@@ -3245,13 +3245,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>150</v>
+        <v>123</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3302,13 +3302,13 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>73</v>
@@ -3319,10 +3319,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3333,7 +3333,7 @@
         <v>74</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>73</v>
@@ -3345,13 +3345,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>80</v>
+        <v>123</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3402,13 +3402,13 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>73</v>
@@ -3419,10 +3419,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3430,10 +3430,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>73</v>
@@ -3445,13 +3445,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3502,13 +3502,13 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>73</v>
@@ -3519,10 +3519,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3530,10 +3530,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>73</v>
@@ -3545,13 +3545,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3602,13 +3602,13 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>73</v>
@@ -3619,10 +3619,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3630,10 +3630,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>73</v>
@@ -3645,13 +3645,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>159</v>
+        <v>123</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3702,13 +3702,13 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>73</v>
@@ -3719,10 +3719,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3730,10 +3730,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>73</v>
@@ -3745,13 +3745,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3802,13 +3802,13 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>73</v>
@@ -3819,10 +3819,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3830,10 +3830,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>73</v>
@@ -3845,13 +3845,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>83</v>
+        <v>166</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3902,13 +3902,13 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>73</v>
@@ -3919,10 +3919,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -3933,7 +3933,7 @@
         <v>74</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>73</v>
@@ -3945,13 +3945,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>166</v>
+        <v>123</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4002,13 +4002,13 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>73</v>
@@ -4019,10 +4019,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4033,7 +4033,7 @@
         <v>74</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>73</v>
@@ -4045,13 +4045,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4102,13 +4102,13 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>73</v>
@@ -4119,10 +4119,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4133,7 +4133,7 @@
         <v>74</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>73</v>
@@ -4145,13 +4145,13 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>87</v>
+        <v>173</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4202,118 +4202,18 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="C34" s="2"/>
-      <c r="D34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E34" s="2"/>
-      <c r="F34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K34" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="L34" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
-      <c r="P34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q34" s="2"/>
-      <c r="R34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="AG34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-medication.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:07:03+00:00</t>
+    <t>2026-04-09T12:24:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-medication.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T12:24:05+00:00</t>
+    <t>2026-04-13T08:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-medication.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T08:58:24+00:00</t>
+    <t>2026-04-13T09:04:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-medication.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:04:52+00:00</t>
+    <t>2026-04-14T07:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-medication.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T07:59:58+00:00</t>
+    <t>2026-04-16T07:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-medication.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-medication.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:11:11+00:00</t>
+    <t>2026-04-24T08:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-medication.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:31:26+00:00</t>
+    <t>2026-04-24T12:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-medication.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T12:30:57+00:00</t>
+    <t>2026-04-24T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
